--- a/Trắc nghiệm ôn luyện/DA Analytics/multiple_choice_sample_template_DATA_VISUALIZATION.xlsx
+++ b/Trắc nghiệm ôn luyện/DA Analytics/multiple_choice_sample_template_DATA_VISUALIZATION.xlsx
@@ -456,13 +456,13 @@
         <v>Biểu đồ tròn (Pie Chart) hoặc Biểu đồ vành khuyên (Donut Chart) — so sánh tỷ lệ phần trăm trên tổng thể</v>
       </c>
       <c r="F2" t="str">
+        <v>Biểu đồ phân tán (Scatter Plot) — phân tích mối tương quan giữa hai biến số</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ dữ liệu</v>
+      </c>
+      <c r="H2" t="str">
         <v>Biểu đồ đường (Line Chart) — theo dõi xu hướng biến động dữ liệu theo thời gian</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Biểu đồ phân tán (Scatter Plot) — phân tích mối tương quan giữa hai biến số</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ dữ liệu</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -482,19 +482,19 @@
         <v>Line Chart là lựa chọn chuẩn mực để hiển thị dữ liệu dạng chuỗi thời gian (Time Series), giúp người xem dễ dàng nhận ra xu hướng (trends), tính chu kỳ (seasonality) của số liệu.</v>
       </c>
       <c r="E3" t="str">
+        <v>Hiển thị mối tương quan giữa cân nặng và chiều cao của các học sinh — mối tương quan hai biến</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Thể hiện mật độ tập trung dân số của các tỉnh thành trên bản đồ địa lý — phân bổ địa lý</v>
+      </c>
+      <c r="G3" t="str">
         <v>Trực quan hóa xu hướng tăng trưởng hoặc suy giảm của dữ liệu liên tục theo thời gian — theo dõi xu hướng thời gian</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>So sánh giá trị rời rạc của 10 cửa hàng khác nhau trong cùng một tháng — so sánh giá trị rời rạc</v>
       </c>
-      <c r="G3" t="str">
-        <v>Hiển thị mối tương quan giữa cân nặng và chiều cao của các học sinh — mối tương quan hai biến</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Thể hiện mật độ tập trung dân số của các tỉnh thành trên bản đồ địa lý — phân bổ địa lý</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Slicer trong PowerBI là bộ lọc giao diện tương tác (như chọn Năm, chọn Khu vực), giúp người xem chủ động lọc dữ liệu trên dashboard theo nhu cầu phân tích tức thời.</v>
       </c>
       <c r="E4" t="str">
+        <v>Là thuật toán dùng để nén kích thước của các hình ảnh biểu đồ cho nhẹ báo cáo — nén ảnh biểu đồ</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Là biểu đồ dùng để hiển thị sơ đồ phân cấp nhân sự của doanh nghiệp — sơ đồ nhân sự</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Là công cụ dùng để cắt nhỏ file báo cáo ra thành nhiều tệp tin PDF độc lập — cắt nhỏ báo cáo</v>
+      </c>
+      <c r="H4" t="str">
         <v>Là bộ lọc trực quan cho phép người dùng tương tác bấm chọn để lọc dữ liệu hiển thị trên các biểu đồ khác — bộ lọc tương tác</v>
       </c>
-      <c r="F4" t="str">
-        <v>Là công cụ dùng để cắt nhỏ file báo cáo ra thành nhiều tệp tin PDF độc lập — cắt nhỏ báo cáo</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Là thuật toán dùng để nén kích thước của các hình ảnh biểu đồ cho nhẹ báo cáo — nén ảnh biểu đồ</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Là biểu đồ dùng để hiển thị sơ đồ phân cấp nhân sự của doanh nghiệp — sơ đồ nhân sự</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -569,19 +569,19 @@
         <v>Scatter Plot (Biểu đồ phân tán) hiển thị các giá trị dưới dạng các điểm chấm trên trục X và Y. Xu hướng phân bổ của các dấu chấm giúp nhận diện mối quan hệ tương quan tuyến tính (dương, âm hoặc không tương quan).</v>
       </c>
       <c r="E6" t="str">
+        <v>Biểu đồ cột chồng (Stacked Bar Chart) — so sánh các phần tử trong tổng số</v>
+      </c>
+      <c r="F6" t="str">
         <v>Biểu đồ phân tán (Scatter Plot) — biểu thị các cặp điểm dữ liệu trên hệ tọa độ đề-các</v>
       </c>
-      <c r="F6" t="str">
-        <v>Biểu đồ cột chồng (Stacked Bar Chart) — so sánh các phần tử trong tổng số</v>
-      </c>
       <c r="G6" t="str">
+        <v>Biểu đồ phễu (Funnel Chart) — theo dõi quy trình chuyển đổi khách hàng</v>
+      </c>
+      <c r="H6" t="str">
         <v>Biểu đồ tròn (Pie Chart) — so sánh tỷ lệ phần trăm đóng góp</v>
       </c>
-      <c r="H6" t="str">
-        <v>Biểu đồ phễu (Funnel Chart) — theo dõi quy trình chuyển đổi khách hàng</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Nguyên tắc của Edward Tufte khuyên tối đa hóa Data-to-Ink ratio. Nghĩa là phần lớn lượng "mực" (màu sắc, pixel trên màn hình) dùng để vẽ biểu đồ phải đại diện trực tiếp cho dữ liệu, tránh trang trí rườm rà (chartjunk) gây xao nhãng.</v>
       </c>
       <c r="E7" t="str">
+        <v>Chỉ hiển thị số liệu dưới dạng bảng văn bản thô đen trắng không có biểu đồ — tối giản hóa cực đoan</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Bắt buộc phải in tất cả các báo cáo ra giấy bằng mực in màu chất lượng cao nhất — in ấn vật lý báo cáo</v>
+      </c>
+      <c r="G7" t="str">
         <v>Tối giản hóa thiết kế bằng cách loại bỏ các yếu tố đồ họa thừa thãi (đường lưới quá đậm, hình vẽ 3D, viền bảng) để tập trung làm nổi bật dữ liệu chính — tối đa hóa hiển thị dữ liệu sạch</v>
       </c>
-      <c r="F7" t="str">
+      <c r="H7" t="str">
         <v>Tăng cường sử dụng nhiều màu sắc rực rỡ và hình vẽ minh họa để lấp đầy khoảng trắng của biểu đồ — tăng mực in trang trí</v>
       </c>
-      <c r="G7" t="str">
-        <v>Bắt buộc phải in tất cả các báo cáo ra giấy bằng mực in màu chất lượng cao nhất — in ấn vật lý báo cáo</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Chỉ hiển thị số liệu dưới dạng bảng văn bản thô đen trắng không có biểu đồ — tối giản hóa cực đoan</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -659,13 +659,13 @@
         <v>Hiển thị một con số thống kê quan trọng duy nhất (như Tổng doanh thu, Số khách hàng mới) một cách nổi bật để người dùng dễ đọc nhanh — hiển thị chỉ số cốt lõi</v>
       </c>
       <c r="F9" t="str">
+        <v>Bảng danh sách tất cả các công việc hàng ngày của lập trình viên — danh sách tác vụ</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Biểu đồ hình cột thể hiện mức lương trung bình của nhân viên trong công ty — biểu đồ lương</v>
+      </c>
+      <c r="H9" t="str">
         <v>Dùng để khách hàng quẹt thẻ thanh toán chi phí mua hàng trực tiếp trên website — cổng thanh toán trực quan</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Bảng danh sách tất cả các công việc hàng ngày của lập trình viên — danh sách tác vụ</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Biểu đồ hình cột thể hiện mức lương trung bình của nhân viên trong công ty — biểu đồ lương</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -685,19 +685,19 @@
         <v>Waterfall Chart (Biểu đồ thác nước) cực kỳ hữu ích trong tài chính để giải thích sự thay đổi từ trạng thái A sang trạng thái B thông qua các khoản cộng/trừ trung gian.</v>
       </c>
       <c r="E10" t="str">
+        <v>Biểu đồ mạng nhện (Radar Chart) — hiển thị nhiều thuộc tính trên trục đa hướng</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Biểu đồ bong bóng (Bubble Chart) — hiển thị mối tương quan 3 biến số</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Biểu đồ tròn (Pie Chart) — hiển thị phân bổ phần trăm cố định</v>
+      </c>
+      <c r="H10" t="str">
         <v>Biểu đồ thác nước (Waterfall Chart) — hiển thị các cột nổi biểu thị sự tăng giảm và cột chốt tổng kết</v>
       </c>
-      <c r="F10" t="str">
-        <v>Biểu đồ tròn (Pie Chart) — hiển thị phân bổ phần trăm cố định</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Biểu đồ mạng nhện (Radar Chart) — hiển thị nhiều thuộc tính trên trục đa hướng</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Biểu đồ bong bóng (Bubble Chart) — hiển thị mối tương quan 3 biến số</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>M-Code (Power Query Formula Language) dùng ở khâu chuẩn bị dữ liệu (Query Editor) để làm sạch, pivot, merge bảng trước khi load vào model. DAX (Data Analysis Expressions) dùng sau khi dữ liệu đã được load để tạo các Measures/Calculated Columns phục vụ vẽ biểu đồ.</v>
       </c>
       <c r="E11" t="str">
+        <v>M-Code chỉ chạy trên hệ điều hành MacOS; còn DAX chỉ chạy trên Windows — hệ điều hành hỗ trợ</v>
+      </c>
+      <c r="F11" t="str">
+        <v>M-Code dùng để vẽ các biểu đồ 3D phức tạp; còn DAX dùng để thiết kế màu sắc báo cáo — tính năng đồ họa</v>
+      </c>
+      <c r="G11" t="str">
+        <v>M-Code bắt buộc phải compile thành file chạy `.exe` trước khi sử dụng trong PowerBI — cơ chế biên dịch</v>
+      </c>
+      <c r="H11" t="str">
         <v>M-Code viết trong Power Query để biến đổi dữ liệu (ETL); DAX viết trong Data Model để tính toán phân tích (Data Analysis) — ETL dữ liệu đầu vào vs tính toán phân tích</v>
       </c>
-      <c r="F11" t="str">
-        <v>M-Code chỉ chạy trên hệ điều hành MacOS; còn DAX chỉ chạy trên Windows — hệ điều hành hỗ trợ</v>
-      </c>
-      <c r="G11" t="str">
-        <v>M-Code dùng để vẽ các biểu đồ 3D phức tạp; còn DAX dùng để thiết kế màu sắc báo cáo — tính năng đồ họa</v>
-      </c>
-      <c r="H11" t="str">
-        <v>M-Code bắt buộc phải compile thành file chạy `.exe` trước khi sử dụng trong PowerBI — cơ chế biên dịch</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Theo nghiên cứu hành vi đọc (Eye-tracking), mắt người dùng có xu hướng quét màn hình từ trái sang phải và từ trên xuống dưới (theo hình chữ Z hoặc F). Vì vậy, góc trên bên trái là "bất động sản vàng", nơi đặt các thông tin quan trọng nhất.</v>
       </c>
       <c r="E12" t="str">
+        <v>Ẩn sâu trong menu cài đặt cấu hình của báo cáo — menu cấu hình</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Chính giữa trung tâm của trang Dashboard — vị trí trung tâm</v>
+      </c>
+      <c r="G12" t="str">
         <v>Góc trên bên trái của trang Dashboard — tiêu điểm mắt đọc đầu tiên</v>
       </c>
-      <c r="F12" t="str">
+      <c r="H12" t="str">
         <v>Góc dưới cùng bên phải của trang Dashboard — vị trí kết thúc trang</v>
       </c>
-      <c r="G12" t="str">
-        <v>Chính giữa trung tâm của trang Dashboard — vị trí trung tâm</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Ẩn sâu trong menu cài đặt cấu hình của báo cáo — menu cấu hình</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -772,10 +772,10 @@
         <v>Dual-axis Chart (hoặc Line and Stacked Column Chart) cho phép hiển thị đồng thời hai biến có đơn vị và quy mô khác nhau trên cùng một trục X, giúp so sánh mối quan hệ xu hướng giữa chúng.</v>
       </c>
       <c r="E13" t="str">
+        <v>Cộng thêm 1,000,000 vào tất cả các giá trị tỷ lệ phần trăm để đưa chúng lên cùng quy mô — cộng hằng số sai lệch dữ liệu</v>
+      </c>
+      <c r="F13" t="str">
         <v>Sử dụng biểu đồ trục kép (Dual-axis / Combo Chart) với hai trục Y độc lập (trục trái cho số lượng, trục phải cho tỷ lệ) — biểu đồ trục kép</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Cộng thêm 1,000,000 vào tất cả các giá trị tỷ lệ phần trăm để đưa chúng lên cùng quy mô — cộng hằng số sai lệch dữ liệu</v>
       </c>
       <c r="G13" t="str">
         <v>Vẽ hai biểu đồ đường độc lập xếp chồng lên nhau ở hai trang báo cáo khác nhau — phân tách trang báo cáo</v>
@@ -784,7 +784,7 @@
         <v>Chuyển trục giá trị của tỷ lệ mua hàng sang thang đo logarit bắt đầu từ số âm — thang đo logarit sai quy chuẩn</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>RLS cho phép định nghĩa các bộ lọc (DAX filter) gắn với các Role. Khi người dùng đăng nhập xem báo cáo, PowerBI tự động áp bộ lọc tương ứng để lọc dữ liệu ở tầng database, đảm bảo an toàn thông tin mà chỉ cần thiết kế duy nhất một file dashboard.</v>
       </c>
       <c r="E14" t="str">
-        <v>Giới hạn dữ liệu hiển thị trên báo cáo cho từng người dùng dựa trên vai trò của họ (ví dụ: Giám đốc miền Nam chỉ xem được dữ liệu miền Nam) — bảo mật phân quyền dữ liệu theo dòng</v>
+        <v>Tự động khóa tài khoản đăng nhập của người dùng nếu họ chụp ảnh màn hình báo cáo — ngăn chặn chụp ảnh</v>
       </c>
       <c r="F14" t="str">
-        <v>Tự động khóa tài khoản đăng nhập của người dùng nếu họ chụp ảnh màn hình báo cáo — ngăn chặn chụp ảnh</v>
+        <v>Mã hóa toàn bộ các ô dữ liệu chứa số tiền giao dịch thành dạng ký tự dấu sao (*) — ẩn thông tin số tiền</v>
       </c>
       <c r="G14" t="str">
         <v>Tăng tốc độ load của các câu lệnh truy vấn dữ liệu SQL lên nhanh gấp 10 lần — tối ưu hóa tốc độ</v>
       </c>
       <c r="H14" t="str">
-        <v>Mã hóa toàn bộ các ô dữ liệu chứa số tiền giao dịch thành dạng ký tự dấu sao (*) — ẩn thông tin số tiền</v>
+        <v>Giới hạn dữ liệu hiển thị trên báo cáo cho từng người dùng dựa trên vai trò của họ (ví dụ: Giám đốc miền Nam chỉ xem được dữ liệu miền Nam) — bảo mật phân quyền dữ liệu theo dòng</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Với nhãn danh mục dài (ví dụ: "Thiết bị điện tử gia dụng"), nếu vẽ cột dọc, nhãn sẽ bị viết chéo hoặc viết dọc rất khó đọc. Biểu đồ cột ngang cung cấp không gian rộng bên trái để nhãn hiển thị thẳng thớm, dễ đọc từ trái sang phải.</v>
       </c>
       <c r="E15" t="str">
-        <v>Khi số lượng danh mục so sánh nhiều (trên 10) hoặc tên nhãn của các danh mục quá dài để hiển thị trên trục hoành — nhãn dài và số lượng danh mục lớn</v>
+        <v>Khi cần hiển thị xu hướng biến động liên tục của doanh thu theo thời gian — theo dõi xu hướng thời gian</v>
       </c>
       <c r="F15" t="str">
         <v>Khi dữ liệu so sánh chứa các giá trị số âm và số dương xen kẽ nhau — giá trị âm dương xen kẽ</v>
       </c>
       <c r="G15" t="str">
-        <v>Khi cần hiển thị xu hướng biến động liên tục của doanh thu theo thời gian — theo dõi xu hướng thời gian</v>
+        <v>Khi biểu đồ bắt buộc phải hiển thị trên màn hình tivi xoay dọc 90 độ — xoay màn hình tivi</v>
       </c>
       <c r="H15" t="str">
-        <v>Khi biểu đồ bắt buộc phải hiển thị trên màn hình tivi xoay dọc 90 độ — xoay màn hình tivi</v>
+        <v>Khi số lượng danh mục so sánh nhiều (trên 10) hoặc tên nhãn của các danh mục quá dài để hiển thị trên trục hoành — nhãn dài và số lượng danh mục lớn</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>Chartjunk làm tăng tải nhận thức của người xem mà không đem lại thông tin hữu ích nào. Nguyên tắc thiết kế hiện đại hướng tới sự sạch sẽ, trực quan, loại bỏ chartjunk để dữ liệu tự lên tiếng.</v>
       </c>
       <c r="E16" t="str">
-        <v>Các yếu tố trang trí không mang giá trị thông tin dữ liệu (như hình nền lòe loẹt, viền đậm, đổ bóng 3D, họa tiết kẻ sọc) gây mất tập trung — yếu tố trang trí thừa gây nhiễu</v>
+        <v>Các câu lệnh SQL bị viết lỗi cú pháp nằm trong tệp tin nháp của lập trình viên — câu lệnh SQL nháp</v>
       </c>
       <c r="F16" t="str">
         <v>Các file báo cáo cũ đã bị xóa bỏ và nằm trong thùng rác của máy tính — file báo cáo cũ trong thùng rác</v>
       </c>
       <c r="G16" t="str">
-        <v>Các câu lệnh SQL bị viết lỗi cú pháp nằm trong tệp tin nháp của lập trình viên — câu lệnh SQL nháp</v>
+        <v>Các yếu tố trang trí không mang giá trị thông tin dữ liệu (như hình nền lòe loẹt, viền đậm, đổ bóng 3D, họa tiết kẻ sọc) gây mất tập trung — yếu tố trang trí thừa gây nhiễu</v>
       </c>
       <c r="H16" t="str">
         <v>Các biểu đồ hiển thị sai lệch số dư tài khoản thực tế của khách hàng — biểu đồ sai số liệu</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Quá nhiều màu sắc sẽ làm người dùng mất tập trung và không biết đâu là điểm nhấn. Nên sử dụng màu chủ đạo thương hiệu (Brand colors), màu trung tính (Neutral - xám, trắng) làm nền, và dùng màu tương phản mạnh (như cam, đỏ) làm điểm nhấn cho các dữ liệu bất thường.</v>
       </c>
       <c r="E17" t="str">
+        <v>Tô mỗi cột biểu đồ bằng một màu sắc ngẫu nhiên khác nhau để tạo sự sặc sỡ cuốn hút — sặc sỡ ngẫu nhiên</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Chỉ sử dụng duy nhất màu đỏ và màu xanh lá cây cho toàn bộ các biểu đồ trên dashboard — giới hạn đỏ xanh</v>
+      </c>
+      <c r="G17" t="str">
         <v>Sử dụng tối đa 3-5 màu sắc trong một bảng màu nhất quán, kết hợp các sắc độ đậm nhạt (Saturation/Value) của cùng một màu để phân biệt dữ liệu — bảng màu nhất quán giới hạn</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Tô mỗi cột biểu đồ bằng một màu sắc ngẫu nhiên khác nhau để tạo sự sặc sỡ cuốn hút — sặc sỡ ngẫu nhiên</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Chỉ sử dụng duy nhất màu đỏ và màu xanh lá cây cho toàn bộ các biểu đồ trên dashboard — giới hạn đỏ xanh</v>
       </c>
       <c r="H17" t="str">
         <v>Sử dụng các màu sắc phản quang (Neon) trên nền đen để tạo hiệu ứng phát sáng — màu phản quang</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -917,10 +917,10 @@
         <v>Import Mode nén dữ liệu cực tốt và chạy rất nhanh trên bộ nhớ RAM (VertiPaq engine) nhưng dung lượng file bị giới hạn (1GB cho bản Pro) và cần thiết lập lịch làm mới (Refresh schedule). DirectQuery không giới hạn dung lượng file báo cáo và cập nhật dữ liệu real-time, nhưng hiệu năng phụ thuộc hoàn toàn vào tốc độ của database nguồn.</v>
       </c>
       <c r="E18" t="str">
+        <v>Import chỉ hỗ trợ kết nối với file Excel; DirectQuery chỉ hỗ trợ kết nối với cơ sở dữ liệu MySQL — phân loại nguồn kết nối</v>
+      </c>
+      <c r="F18" t="str">
         <v>Import: Nạp toàn bộ dữ liệu vào bộ nhớ trong của PowerBI (nhanh, tốn RAM); DirectQuery: Không nạp dữ liệu, truy vấn trực tiếp từ database nguồn mỗi khi tương tác biểu đồ (chậm hơn, dữ liệu thời gian thực) — nạp bộ nhớ vs truy vấn trực tiếp thời gian thực</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Import chỉ hỗ trợ kết nối với file Excel; DirectQuery chỉ hỗ trợ kết nối với cơ sở dữ liệu MySQL — phân loại nguồn kết nối</v>
       </c>
       <c r="G18" t="str">
         <v>Import bắt buộc phải có tài khoản VIP của Microsoft; DirectQuery hoàn toàn miễn phí cho tất cả mọi người — chi phí bản quyền</v>
@@ -929,7 +929,7 @@
         <v>Import tự động mã hóa dữ liệu; DirectQuery tự động xóa dữ liệu trùng lặp khi nạp — cơ chế tự động dữ liệu</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Moving Average (Trung bình trượt) giúp lọc bỏ các biến động nhiễu ngắn hạn (noise). Ví dụ, đường trung bình động 12 tháng sẽ cộng doanh thu của 12 tháng gần nhất và chia đều, giúp nhìn rõ xu hướng tăng trưởng thực tế (trend) qua các năm bất chấp sự trồi sụt của mùa vụ.</v>
       </c>
       <c r="E19" t="str">
+        <v>Tự động làm tròn tất cả các con số doanh thu hàng tháng về mức trung bình cộng của cả năm — làm tròn trung bình năm</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Xóa bỏ toàn bộ các tháng có doanh số quá thấp hoặc quá cao ra khỏi biểu đồ — lọc bỏ dữ liệu biến động cực đoan</v>
+      </c>
+      <c r="G19" t="str">
         <v>Vẽ thêm đường trung bình động (Moving Average - ví dụ đường trung bình 3 tháng hoặc 12 tháng) đè lên biểu đồ đường gốc — đường trung bình động (Moving Average)</v>
       </c>
-      <c r="F19" t="str">
+      <c r="H19" t="str">
         <v>Chuyển đổi toàn bộ biểu đồ đường sang biểu đồ tròn để triệt tiêu trục thời gian — triệt tiêu thời gian</v>
       </c>
-      <c r="G19" t="str">
-        <v>Tự động làm tròn tất cả các con số doanh thu hàng tháng về mức trung bình cộng của cả năm — làm tròn trung bình năm</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Xóa bỏ toàn bộ các tháng có doanh số quá thấp hoặc quá cao ra khỏi biểu đồ — lọc bỏ dữ liệu biến động cực đoan</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Đối với dữ liệu khổng lồ, việc gọi DirectQuery quét 500 triệu dòng mỗi lần click filter là thảm họa hiệu năng. Giải pháp chuẩn là tạo các bảng tổng hợp (Aggregated Tables - ví dụ: tổng hợp doanh số theo Ngày-Cửa hàng thay vì lưu từng hóa đơn chi tiết). Trong PowerBI, thiết lập cơ chế tự động định tuyến truy vấn: Nếu người dùng xem tổng quan, PowerBI sẽ lấy từ bảng Aggregation (chạy cực nhanh); nếu người dùng drill-down xem chi tiết hóa đơn, hệ thống mới gọi DirectQuery quét bảng chi tiết.</v>
       </c>
       <c r="E20" t="str">
+        <v>Giảm bớt số lượng màu sắc hiển thị trên các biểu đồ tròn và cột của báo cáo — giảm màu sắc vô nghĩa</v>
+      </c>
+      <c r="F20" t="str">
         <v>Tạo các bảng tổng hợp (Aggregations) ở mức độ cao trong database nguồn, thiết lập cơ chế Dual/Import cho bảng tổng hợp đó trong PowerBI; đồng thời tối ưu hóa Index trong SQL Server — sử dụng bảng tổng hợp và tối ưu hóa index</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
+        <v>Yêu cầu lập trình viên viết code khóa tính năng lọc tương tác (Slicers) của người dùng trên dashboard — khóa tính năng bộ lọc</v>
+      </c>
+      <c r="H20" t="str">
         <v>Chuyển đổi kết nối sang dạng Import Mode và nâng cấp ổ cứng của tất cả máy tính người dùng lên SSD 2TB — nâng cấp phần cứng cục bộ</v>
       </c>
-      <c r="G20" t="str">
-        <v>Giảm bớt số lượng màu sắc hiển thị trên các biểu đồ tròn và cột của báo cáo — giảm màu sắc vô nghĩa</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Yêu cầu lập trình viên viết code khóa tính năng lọc tương tác (Slicers) của người dùng trên dashboard — khóa tính năng bộ lọc</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Radar Chart rất tốt để hiển thị profile năng lực đa chiều (multivariate profile). Tuy nhiên, nó có nhược điểm lớn về mặt UX: Con người rất khó so sánh diện tích của các hình đa giác chồng lên nhau. Thứ tự đặt các trục năng lực xung quanh vòng tròn cũng làm thay đổi hình dáng đa giác, gây hiểu lầm trực quan.</v>
       </c>
       <c r="E21" t="str">
+        <v>Biểu đồ bong bóng (Bubble Chart); hạn chế lớn nhất là không thể hiển thị được các giá trị số nguyên — không hiển thị số nguyên</v>
+      </c>
+      <c r="F21" t="str">
         <v>Biểu đồ radar (Radar / Spider Chart); hạn chế lớn nhất là khó so sánh chính xác diện tích chồng lấn giữa các nhân viên và dễ bị biến dạng trực quan tùy thuộc vào thứ tự sắp xếp các trục — biểu đồ radar và hạn chế diện tích chồng lấn</v>
       </c>
-      <c r="F21" t="str">
-        <v>Biểu đồ bong bóng (Bubble Chart); hạn chế lớn nhất là không thể hiển thị được các giá trị số nguyên — không hiển thị số nguyên</v>
-      </c>
       <c r="G21" t="str">
+        <v>Biểu đồ cột chồng 100% (100% Stacked Bar Chart); hạn chế lớn nhất là bắt buộc tổng các tiêu chí năng lực phải bằng đúng 100 — giới hạn tổng số 100</v>
+      </c>
+      <c r="H21" t="str">
         <v>Biểu đồ bản đồ nhiệt (Heatmap); hạn chế lớn nhất là không thể chạy được trên các thiết bị di động chạy iOS — giới hạn hệ điều hành di động</v>
       </c>
-      <c r="H21" t="str">
-        <v>Biểu đồ cột chồng 100% (100% Stacked Bar Chart); hạn chế lớn nhất là bắt buộc tổng các tiêu chí năng lực phải bằng đúng 100 — giới hạn tổng số 100</v>
-      </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Row Context duyệt qua từng dòng nhưng KHÔNG tự động lọc dữ liệu của các bảng có liên kết. Filter Context là bộ lọc thực tế đang áp dụng lên Data Model. Để chuyển đổi Row Context thành Filter Context (ví dụ để tính tổng doanh thu của khách hàng hiện tại khi duyệt bảng), ta phải bọc công thức trong hàm `CALCULATE` (gọi là Context Transition).</v>
       </c>
       <c r="E22" t="str">
+        <v>Row Context chỉ áp dụng cho dữ liệu kiểu chuỗi; còn Filter Context chỉ áp dụng cho dữ liệu kiểu ngày tháng — phân loại theo kiểu dữ liệu</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Row Context làm tăng tốc độ tải trang; còn Filter Context làm giảm dung lượng file báo cáo — tác động hiệu năng</v>
+      </c>
+      <c r="G22" t="str">
         <v>Row Context áp dụng khi duyệt qua từng dòng của bảng (như trong Calculated Column hoặc các hàm vòng lặp dạng X); Filter Context áp dụng bởi các bộ lọc trên báo cáo (slicers, biểu đồ, hàm CALCULATE) tác động lên tập dữ liệu nạp vào phép tính — phân biệt cơ chế lọc dữ liệu DAX</v>
       </c>
-      <c r="F22" t="str">
-        <v>Row Context chỉ áp dụng cho dữ liệu kiểu chuỗi; còn Filter Context chỉ áp dụng cho dữ liệu kiểu ngày tháng — phân loại theo kiểu dữ liệu</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Row Context do hệ thống tự sinh; còn Filter Context bắt buộc lập trình viên phải khai báo thủ công bằng SQL — phân biệt chủ thể tạo</v>
       </c>
-      <c r="H22" t="str">
-        <v>Row Context làm tăng tốc độ tải trang; còn Filter Context làm giảm dung lượng file báo cáo — tác động hiệu năng</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Alert Fatigue xảy ra khi hệ thống báo động quá nhiều đối với các biến động bình thường (noise). Biểu đồ SPC sử dụng toán thống kê để phân biệt biến động ngẫu nhiên (Common cause variation - không cần báo động) và biến động bất thường (Special cause variation - vượt biên UCL/LCL - bắt buộc phải báo động và xử lý).</v>
       </c>
       <c r="E23" t="str">
+        <v>Thiết kế tất cả các chỉ số trên dashboard đều hiển thị màu đỏ nhấp nháy để bắt buộc nhân viên phải chú ý liên tục — cảnh báo đỏ toàn diện gây nhiễu</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Ẩn toàn bộ các chỉ số cảnh báo đi, khi nào sự cố thực sự xảy ra thì hệ thống tự động khóa màn hình của người dùng — ẩn cảnh báo khóa màn hình</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Yêu cầu hệ thống gửi tin nhắn SMS cảnh báo đến điện thoại của giám đốc bệnh viện cứ sau mỗi 5 phút — gửi SMS liên tục</v>
+      </c>
+      <c r="H23" t="str">
         <v>Thiết kế biểu đồ kiểm soát quy trình bằng thống kê (SPC Chart - Statistical Process Control) với các đường biên giới hạn trên/dưới (UCL/LCL); chỉ kích hoạt cảnh báo đỏ hoặc gửi thông báo khi dữ liệu vượt quá các biên giới hạn thống kê này hoặc có xu hướng lệch biên liên tục — biểu đồ kiểm soát thống kê SPC</v>
       </c>
-      <c r="F23" t="str">
-        <v>Thiết kế tất cả các chỉ số trên dashboard đều hiển thị màu đỏ nhấp nháy để bắt buộc nhân viên phải chú ý liên tục — cảnh báo đỏ toàn diện gây nhiễu</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Ẩn toàn bộ các chỉ số cảnh báo đi, khi nào sự cố thực sự xảy ra thì hệ thống tự động khóa màn hình của người dùng — ẩn cảnh báo khóa màn hình</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Yêu cầu hệ thống gửi tin nhắn SMS cảnh báo đến điện thoại của giám đốc bệnh viện cứ sau mỗi 5 phút — gửi SMS liên tục</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1094,10 +1094,10 @@
         <v>Viết trực tiếp trong CALCULATE là viết tắt (syntax sugar), PowerBI sẽ tự động chuyển đổi thành hàm FILTER tối ưu trên các cột; sử dụng hàm FILTER(table, ...) duyệt qua toàn bộ bảng vật lý sẽ rất chậm nếu bảng lớn — tối ưu hóa ngữ cảnh lọc cột vs duyệt bảng</v>
       </c>
       <c r="F24" t="str">
+        <v>FILTER bắt buộc phải trả về kiểu dữ liệu số nguyên; còn CALCULATE bắt buộc phải trả về kiểu dữ liệu boolean — kiểu dữ liệu trả về</v>
+      </c>
+      <c r="G24" t="str">
         <v>FILTER chỉ chạy được trên các bảng có ít hơn 100 dòng; còn viết trực tiếp trong CALCULATE hỗ trợ bảng vô hạn — giới hạn kích thước bảng</v>
-      </c>
-      <c r="G24" t="str">
-        <v>FILTER bắt buộc phải trả về kiểu dữ liệu số nguyên; còn CALCULATE bắt buộc phải trả về kiểu dữ liệu boolean — kiểu dữ liệu trả về</v>
       </c>
       <c r="H24" t="str">
         <v>FILTER chạy nhanh gấp 10 lần so với CALCULATE do không tốn tài nguyên chuyển đổi ngữ cảnh — so sánh tốc độ chạy</v>
@@ -1120,19 +1120,19 @@
         <v>Sankey Diagram là công cụ hoàn hảo để trực quan hóa dòng chảy (flows) năng lượng, vật liệu hoặc chi phí. Độ rộng của các luồng liên kết (links) thể hiện trực quan lưu lượng, giúp dễ dàng nhận ra các điểm nghẽn (bottlenecks) hoặc thất thoát trong hệ thống.</v>
       </c>
       <c r="E25" t="str">
+        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ theo tọa độ</v>
+      </c>
+      <c r="F25" t="str">
         <v>Biểu đồ Sankey (Sankey Diagram) — trực quan hóa luồng dòng chảy với độ rộng của nhánh tỷ lệ thuận với lưu lượng</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
+        <v>Biểu đồ radar (Radar Chart) — trực quan hóa cấu trúc năng lực đa chiều</v>
+      </c>
+      <c r="H25" t="str">
         <v>Biểu đồ cột chồng 100% (100% Stacked Column Chart) — trực quan hóa tỷ lệ phần trăm phân bổ</v>
       </c>
-      <c r="G25" t="str">
-        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ theo tọa độ</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Biểu đồ radar (Radar Chart) — trực quan hóa cấu trúc năng lực đa chiều</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Các hàm Time Intelligence của DAX hoạt động dựa trên giả định rằng bảng ngày tháng là liên tục (không mất ngày nào kể cả ngày lễ, cuối tuần). Nếu bảng giao dịch (Sales Table) bị mất ngày không có giao dịch, việc gọi các hàm dịch chuyển thời gian (như so sánh cùng kỳ năm ngoái) trực tiếp trên cột ngày của Sales Table sẽ tính toán sai lệch hoặc báo lỗi.</v>
       </c>
       <c r="E26" t="str">
+        <v>Vì nếu không tạo bảng Date độc lập, PowerBI sẽ không cho phép người dùng vẽ biểu đồ đường theo thời gian — giới hạn vẽ biểu đồ</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Để hệ thống tự động mã hóa toàn bộ dữ liệu thời gian tránh sự tấn công của hacker — bảo mật dữ liệu thời gian</v>
+      </c>
+      <c r="G26" t="str">
         <v>Để đảm bảo bảng chứa một chuỗi ngày liên tục không bị ngắt quãng (không có khoảng trống ngày) và có kiểu dữ liệu Datetime chuẩn, làm cơ sở cho các thuật toán dịch chuyển thời gian của DAX hoạt động chính xác — yêu cầu chuỗi ngày liên tục chuẩn hóa</v>
       </c>
-      <c r="F26" t="str">
+      <c r="H26" t="str">
         <v>Để PowerBI tự động gửi email báo cáo doanh thu vào ngày cuối cùng của mỗi tháng tài chính — tự động gửi báo cáo tháng</v>
       </c>
-      <c r="G26" t="str">
-        <v>Để hệ thống tự động mã hóa toàn bộ dữ liệu thời gian tránh sự tấn công của hacker — bảo mật dữ liệu thời gian</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Vì nếu không tạo bảng Date độc lập, PowerBI sẽ không cho phép người dùng vẽ biểu đồ đường theo thời gian — giới hạn vẽ biểu đồ</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
